--- a/frontend/public/templates/Inbound_Order_Import_Template.xlsx
+++ b/frontend/public/templates/Inbound_Order_Import_Template.xlsx
@@ -399,22 +399,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:F4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
         <v>Warehouse Code *</v>
       </c>
       <c r="B1" t="str">
+        <v>Vehicle Number *</v>
+      </c>
+      <c r="C1" t="str">
         <v>Reference No *</v>
       </c>
-      <c r="C1" t="str">
+      <c r="D1" t="str">
         <v>Supplier Name</v>
       </c>
-      <c r="D1" t="str">
+      <c r="E1" t="str">
         <v>SKU Code *</v>
       </c>
-      <c r="E1" t="str">
+      <c r="F1" t="str">
         <v>Expected Qty *</v>
       </c>
     </row>
@@ -423,15 +426,18 @@
         <v>TN01</v>
       </c>
       <c r="B2" t="str">
+        <v>TN01AB1234</v>
+      </c>
+      <c r="C2" t="str">
         <v>PO-1001</v>
       </c>
-      <c r="C2" t="str">
+      <c r="D2" t="str">
         <v>Acme Tyres Pvt Ltd</v>
       </c>
-      <c r="D2" t="str">
+      <c r="E2" t="str">
         <v>TYRE-165-70-R14</v>
       </c>
-      <c r="E2">
+      <c r="F2">
         <v>200</v>
       </c>
     </row>
@@ -440,15 +446,18 @@
         <v>TN01</v>
       </c>
       <c r="B3" t="str">
+        <v>TN01AB1234</v>
+      </c>
+      <c r="C3" t="str">
         <v>PO-1001</v>
       </c>
-      <c r="C3" t="str">
+      <c r="D3" t="str">
         <v>Acme Tyres Pvt Ltd</v>
       </c>
-      <c r="D3" t="str">
+      <c r="E3" t="str">
         <v>TYRE-185-65-R15</v>
       </c>
-      <c r="E3">
+      <c r="F3">
         <v>100</v>
       </c>
     </row>
@@ -457,28 +466,31 @@
         <v>TN01</v>
       </c>
       <c r="B4" t="str">
+        <v>TN01CD5678</v>
+      </c>
+      <c r="C4" t="str">
         <v>PO-1002</v>
       </c>
-      <c r="C4" t="str">
+      <c r="D4" t="str">
         <v>Beta Auto Parts</v>
       </c>
-      <c r="D4" t="str">
+      <c r="E4" t="str">
         <v>BRAKE-PAD-STD</v>
       </c>
-      <c r="E4">
+      <c r="F4">
         <v>500</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -507,29 +519,34 @@
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>2. This mirrors the manual "+ New Order" form exactly — there is no Staging Location column. Staging is chosen later, once the vehicle is actually at the dock (Match Order), never at order-creation time.</v>
+        <v>2. Vehicle Number is required (added 2026-08-27) — every order names exactly ONE vehicle, and that vehicle must already be registered (Gate &amp; Yard → Register Vehicle) before importing. A vehicle can only have ONE unmatched order at a time; importing a second order for a vehicle that already has one pending will fail that row.</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>3. A Reference No must be unique per Warehouse — re-importing a PO number that already exists for that warehouse will fail that order (and only that order; other orders in the same file still import).</v>
+        <v>3. This mirrors the manual "+ New Order" form exactly — there is no Staging Location column. Staging is chosen later, once the vehicle is actually at the dock (Match Order), never at order-creation time.</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>4. SKU Code must already exist in the SKU Master for this company — this import does not create SKUs.</v>
+        <v>4. A Reference No must be unique per Warehouse — re-importing a PO number that already exists for that warehouse will fail that order (and only that order; other orders in the same file still import).</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>5. SKU Code must already exist in the SKU Master for this company — this import does not create SKUs.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A9"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -555,51 +572,62 @@
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Reference No *</v>
+        <v>Vehicle Number *</v>
       </c>
       <c r="B3" t="str">
         <v>Yes, every row</v>
       </c>
       <c r="C3" t="str">
-        <v>The PO/Invoice number. Must be unique per Warehouse — a duplicate (Warehouse + Reference No already on file) blocks that whole order.</v>
+        <v>Must match an already-registered Vehicle for this company (Gate &amp; Yard → Register Vehicle). That vehicle must not already have another unmatched order.</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Supplier Name</v>
+        <v>Reference No *</v>
       </c>
       <c r="B4" t="str">
-        <v>No</v>
+        <v>Yes, every row</v>
       </c>
       <c r="C4" t="str">
-        <v>Free text. Repeat the same value on every row for a given order (only the first row's value is used).</v>
+        <v>The PO/Invoice number. Must be unique per Warehouse — a duplicate (Warehouse + Reference No already on file) blocks that whole order.</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>SKU Code *</v>
+        <v>Supplier Name</v>
       </c>
       <c r="B5" t="str">
-        <v>Yes, every row</v>
+        <v>No</v>
       </c>
       <c r="C5" t="str">
-        <v>Must match an existing SKU Master code for this company.</v>
+        <v>Free text. Repeat the same value on every row for a given order (only the first row's value is used).</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Expected Qty *</v>
+        <v>SKU Code *</v>
       </c>
       <c r="B6" t="str">
         <v>Yes, every row</v>
       </c>
       <c r="C6" t="str">
+        <v>Must match an existing SKU Master code for this company.</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>Expected Qty *</v>
+      </c>
+      <c r="B7" t="str">
+        <v>Yes, every row</v>
+      </c>
+      <c r="C7" t="str">
         <v>A positive number — how much of this SKU is expected on this order.</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C7"/>
   </ignoredErrors>
 </worksheet>
 </file>